--- a/results/DR_results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/anova_env.xlsx
+++ b/results/DR_results/02_taxa_assemblage/Wards_LDA/cluster_classifier/tables/anova_env.xlsx
@@ -486,42 +486,42 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Measured Depth (m)</t>
+          <t>LOI (%)</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>211.87</v>
+        <v>29.44</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>244.11</v>
+        <v>20.73</v>
       </c>
       <c r="F2" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G2" t="n">
-        <v>13.02</v>
+        <v>18.46</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.0001***</t>
+          <t>0.0000***</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>9.08 ± 1.09</t>
+          <t>1.72 ± 0.35</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>3.89 ± 0.62</t>
+          <t>1.38 ± 0.13</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>1.50 ± 0.07</t>
+          <t>4.76 ± 1.18</t>
         </is>
       </c>
     </row>
@@ -535,33 +535,33 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.37</v>
+        <v>0.33</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>0.49</v>
+        <v>0.34</v>
       </c>
       <c r="F3" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G3" t="n">
-        <v>11.3</v>
+        <v>12.59</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0002***</t>
+          <t>0.0001***</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.43 ± 0.04</t>
+          <t>0.41 ± 0.04</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.22 ± 0.03</t>
+          <t>0.19 ± 0.03</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -576,42 +576,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>LOI (%)</t>
+          <t>Measured Depth (m)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>24.42</v>
+        <v>159.24</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>51.87</v>
+        <v>209.91</v>
       </c>
       <c r="F4" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G4" t="n">
-        <v>7.06</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.0031**</t>
+          <t>0.0006***</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.12 ± 0.50</t>
+          <t>8.46 ± 1.01</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>1.71 ± 0.25</t>
+          <t>3.76 ± 0.71</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>4.76 ± 1.18</t>
+          <t>1.50 ± 0.07</t>
         </is>
       </c>
     </row>
@@ -625,33 +625,33 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>21.33</v>
+        <v>21.99</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>93.69</v>
+        <v>84.36</v>
       </c>
       <c r="F5" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G5" t="n">
-        <v>3.41</v>
+        <v>3.39</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.0461*</t>
+          <t>0.0492*</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>18.16 ± 0.67</t>
+          <t>18.07 ± 0.75</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>19.22 ± 0.36</t>
+          <t>19.28 ± 0.39</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -670,33 +670,33 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>6.66</v>
+        <v>5.13</v>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>48.2</v>
+        <v>44.59</v>
       </c>
       <c r="F6" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G6" t="n">
-        <v>2.07</v>
+        <v>1.5</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.1433</t>
+          <t>0.2428</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8.58 ± 0.38</t>
+          <t>8.76 ± 0.38</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>9.12 ± 0.30</t>
+          <t>9.18 ± 0.34</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -715,33 +715,33 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="D7" t="n">
         <v>2</v>
       </c>
       <c r="E7" t="n">
-        <v>24.54</v>
+        <v>20.4</v>
       </c>
       <c r="F7" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="G7" t="n">
-        <v>0.34</v>
+        <v>0.57</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.7142</t>
+          <t>0.5704</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.79 ± 0.29</t>
+          <t>0.65 ± 0.28</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.92 ± 0.20</t>
+          <t>0.77 ± 0.22</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -781,10 +781,10 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="J9" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K9" t="n">
         <v>3</v>
